--- a/data/Анализ отказов.xlsx
+++ b/data/Анализ отказов.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,7 +543,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -567,7 +568,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -592,7 +593,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -617,7 +618,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -642,7 +643,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -667,7 +668,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -692,7 +693,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -717,7 +718,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -742,7 +743,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -792,7 +793,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -817,7 +818,7 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>Фактические материальные затраты</t>
+          <t>Фактические материальные затраты, руб.</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -1010,10 +1011,8 @@
           <t>21 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>11 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H14" s="1" t="n">
+        <v>222.82</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1033,10 +1032,8 @@
           <t>5 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>4 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF14" s="1" t="n">
+        <v>447.82</v>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
@@ -1086,10 +1083,8 @@
           <t>140 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>48 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R16" s="1" t="n">
+        <v>5618.17</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1109,10 +1104,8 @@
           <t>122 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>86 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB16" s="1" t="n">
+        <v>6048.45</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -1132,10 +1125,8 @@
           <t>109 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>86 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG16" s="1" t="n">
+        <v>17355.56</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -1155,10 +1146,8 @@
           <t>125 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>91 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV16" s="1" t="n">
+        <v>29988.6</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
@@ -1178,10 +1167,8 @@
           <t>13 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>5 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF16" s="1" t="n">
+        <v>559.77</v>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
@@ -1231,10 +1218,8 @@
           <t>262 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>158 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA18" s="1" t="n">
+        <v>27726.34</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -1254,10 +1239,8 @@
           <t>36 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>18 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK18" s="1" t="n">
+        <v>962.14</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
@@ -1307,10 +1290,8 @@
           <t>388 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>224 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H20" s="1" t="n">
+        <v>23239</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1330,10 +1311,8 @@
           <t>156 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R20" s="1" t="n">
+        <v>7607.94</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -1353,10 +1332,8 @@
           <t>352 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>161 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ20" s="1" t="n">
+        <v>21668.36</v>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
@@ -1376,10 +1353,8 @@
           <t>188 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>81 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF20" s="1" t="n">
+        <v>9068.280000000001</v>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
@@ -1429,10 +1404,8 @@
           <t>82 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>34 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W22" s="1" t="n">
+        <v>5105.58</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -1452,10 +1425,8 @@
           <t>312 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>108 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB22" s="1" t="n">
+        <v>4020</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -1475,10 +1446,8 @@
           <t>87 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>29 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV22" s="1" t="n">
+        <v>1693.72</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
@@ -1498,10 +1467,8 @@
           <t>323 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>254 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF22" s="1" t="n">
+        <v>17243</v>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
@@ -1521,10 +1488,8 @@
           <t>6 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>4 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK22" s="1" t="n">
+        <v>27594</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
@@ -1574,10 +1539,8 @@
           <t>351 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>152 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ24" s="1" t="n">
+        <v>1870</v>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
@@ -1597,10 +1560,8 @@
           <t>349 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>157 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF24" s="1" t="n">
+        <v>3818.49</v>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
@@ -1650,10 +1611,8 @@
           <t>110 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>76 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R26" s="1" t="n">
+        <v>897.48</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -1673,10 +1632,8 @@
           <t>352 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>252 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ26" s="1" t="n">
+        <v>33915.69</v>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
@@ -1696,10 +1653,8 @@
           <t>190 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF26" s="1" t="n">
+        <v>7277.01</v>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
@@ -1749,10 +1704,8 @@
           <t>154 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>56 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M28" s="1" t="n">
+        <v>22136</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1772,10 +1725,8 @@
           <t>87 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>35 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG28" s="1" t="n">
+        <v>23537</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -1795,10 +1746,8 @@
           <t>43 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>20 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ28" s="1" t="n">
+        <v>8199</v>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
@@ -1818,10 +1767,8 @@
           <t>394 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>205 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV28" s="1" t="n">
+        <v>324</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
@@ -1871,10 +1818,8 @@
           <t>345 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>116 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ30" s="1" t="n">
+        <v>15611.99</v>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
@@ -1924,10 +1869,8 @@
           <t>232 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>124 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H32" s="1" t="n">
+        <v>128374.69</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1947,10 +1890,8 @@
           <t>162 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>64 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M32" s="1" t="n">
+        <v>7724</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -1970,10 +1911,8 @@
           <t>136 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>108 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL32" s="1" t="n">
+        <v>5931.03</v>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
@@ -1993,10 +1932,8 @@
           <t>53 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>21 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF32" s="1" t="n">
+        <v>514.29</v>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
@@ -2172,10 +2109,8 @@
           <t>112 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>36 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H36" s="1" t="n">
+        <v>12954.72</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2195,10 +2130,8 @@
           <t>504 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>395 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M36" s="1" t="n">
+        <v>4788</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2218,10 +2151,8 @@
           <t>341 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>131 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R36" s="1" t="n">
+        <v>15332.93</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -2241,10 +2172,8 @@
           <t>168 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV36" t="inlineStr">
-        <is>
-          <t>116 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV36" s="1" t="n">
+        <v>3824</v>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
@@ -2264,10 +2193,8 @@
           <t>398 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK36" t="inlineStr">
-        <is>
-          <t>230 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK36" s="1" t="n">
+        <v>154.31</v>
       </c>
       <c r="BL36" t="inlineStr">
         <is>
@@ -2317,10 +2244,8 @@
           <t>34 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>15 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H38" s="1" t="n">
+        <v>435</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2340,10 +2265,8 @@
           <t>235 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>134 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M38" s="1" t="n">
+        <v>16241.24</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2363,10 +2286,8 @@
           <t>15 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>9 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R38" s="1" t="n">
+        <v>896</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -2386,10 +2307,8 @@
           <t>35 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>27 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB38" s="1" t="n">
+        <v>195</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -2409,10 +2328,8 @@
           <t>52 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK38" t="inlineStr">
-        <is>
-          <t>31 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK38" s="1" t="n">
+        <v>14700.91</v>
       </c>
       <c r="BL38" t="inlineStr">
         <is>
@@ -2462,10 +2379,8 @@
           <t>88 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>58 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB40" s="1" t="n">
+        <v>891.22</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -2485,10 +2400,8 @@
           <t>18 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF40" t="inlineStr">
-        <is>
-          <t>10 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF40" s="1" t="n">
+        <v>53.33</v>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
@@ -2508,10 +2421,8 @@
           <t>598 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK40" t="inlineStr">
-        <is>
-          <t>201 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK40" s="1" t="n">
+        <v>10743.86</v>
       </c>
       <c r="BL40" t="inlineStr">
         <is>
@@ -2561,10 +2472,8 @@
           <t>353 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>261 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R42" s="1" t="n">
+        <v>32960</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -2584,10 +2493,8 @@
           <t>142 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>86 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG42" s="1" t="n">
+        <v>1782.71</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -2607,10 +2514,8 @@
           <t>397 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>121 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL42" s="1" t="n">
+        <v>4262.5</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -2630,10 +2535,8 @@
           <t>63 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>40 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ42" s="1" t="n">
+        <v>688.52</v>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
@@ -2653,10 +2556,8 @@
           <t>61 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV42" t="inlineStr">
-        <is>
-          <t>22 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV42" s="1" t="n">
+        <v>2180</v>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
@@ -2706,10 +2607,8 @@
           <t>44 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>27 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M44" s="1" t="n">
+        <v>2175</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2729,10 +2628,8 @@
           <t>340 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>118 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB44" s="1" t="n">
+        <v>8299.030000000001</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -2752,10 +2649,8 @@
           <t>129 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV44" t="inlineStr">
-        <is>
-          <t>56 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV44" s="1" t="n">
+        <v>18454.52</v>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
@@ -2775,10 +2670,8 @@
           <t>112 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA44" t="inlineStr">
-        <is>
-          <t>58 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA44" s="1" t="n">
+        <v>10178.02</v>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
@@ -2828,10 +2721,8 @@
           <t>181 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>104 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H46" s="1" t="n">
+        <v>2060.56</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2851,10 +2742,8 @@
           <t>118 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>44 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M46" s="1" t="n">
+        <v>4072.34</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2874,10 +2763,8 @@
           <t>160 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>117 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB46" s="1" t="n">
+        <v>19200</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -2897,10 +2784,8 @@
           <t>45 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>19 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG46" s="1" t="n">
+        <v>622.78</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -2920,10 +2805,8 @@
           <t>177 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>89 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ46" s="1" t="n">
+        <v>22440</v>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
@@ -2943,10 +2826,8 @@
           <t>347 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>273 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF46" s="1" t="n">
+        <v>5610</v>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
@@ -2966,10 +2847,8 @@
           <t>177 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK46" t="inlineStr">
-        <is>
-          <t>55 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK46" s="1" t="n">
+        <v>6475</v>
       </c>
       <c r="BL46" t="inlineStr">
         <is>
@@ -3019,10 +2898,8 @@
           <t>69 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>53 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H48" s="1" t="n">
+        <v>6430.44</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3042,10 +2919,8 @@
           <t>173 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>122 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M48" s="1" t="n">
+        <v>460.75</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3065,10 +2940,8 @@
           <t>25 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>18 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W48" s="1" t="n">
+        <v>2702.96</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -3088,44 +2961,40 @@
           <t>48 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB48" s="1" t="n">
+        <v>323.97</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>14 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>48 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>49 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AQ48" s="1" t="n">
+        <v>122.68</v>
+      </c>
+      <c r="AR48" t="inlineStr">
         <is>
           <t>34 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>14 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>48 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AO48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP48" t="inlineStr">
+      <c r="AS48" t="inlineStr">
         <is>
           <t>49 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>15 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>34 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>49 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
       <c r="BD48" t="n">
         <v>1</v>
       </c>
@@ -3134,10 +3003,8 @@
           <t>194 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>85 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF48" s="1" t="n">
+        <v>6579.93</v>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
@@ -3187,10 +3054,8 @@
           <t>327 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>252 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M50" s="1" t="n">
+        <v>30543.23</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3210,10 +3075,8 @@
           <t>117 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>91 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W50" s="1" t="n">
+        <v>625</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -3233,10 +3096,8 @@
           <t>65 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>39 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ50" s="1" t="n">
+        <v>14840</v>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
@@ -3286,10 +3147,8 @@
           <t>4 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>3 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H52" s="1" t="n">
+        <v>51970</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3309,10 +3168,8 @@
           <t>149 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>95 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R52" s="1" t="n">
+        <v>1190</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -3332,10 +3189,8 @@
           <t>145 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV52" s="1" t="n">
+        <v>3796.28</v>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
@@ -3385,10 +3240,8 @@
           <t>274 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>206 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W54" s="1" t="n">
+        <v>5625</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -3564,10 +3417,8 @@
           <t>100 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>46 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG58" s="1" t="n">
+        <v>953.54</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -3587,10 +3438,8 @@
           <t>33 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>11 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL58" s="1" t="n">
+        <v>387.5</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -3610,10 +3459,8 @@
           <t>371 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>254 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ58" s="1" t="n">
+        <v>4372.13</v>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
@@ -3633,10 +3480,8 @@
           <t>117 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA58" t="inlineStr">
-        <is>
-          <t>77 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA58" s="1" t="n">
+        <v>1708</v>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
@@ -3686,10 +3531,8 @@
           <t>173 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>128 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R60" s="1" t="n">
+        <v>4920</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -3709,10 +3552,8 @@
           <t>47 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>33 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W60" s="1" t="n">
+        <v>3251</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -3732,10 +3573,8 @@
           <t>56 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>21 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ60" s="1" t="n">
+        <v>5100</v>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
@@ -3785,10 +3624,8 @@
           <t>91 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>64 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H62" s="1" t="n">
+        <v>1140.07</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3808,10 +3645,8 @@
           <t>88 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>66 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M62" s="1" t="n">
+        <v>7999.42</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3831,10 +3666,8 @@
           <t>92 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>62 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB62" s="1" t="n">
+        <v>1703.65</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -3854,10 +3687,8 @@
           <t>58 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>40 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG62" s="1" t="n">
+        <v>3944</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -3877,10 +3708,8 @@
           <t>50 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA62" t="inlineStr">
-        <is>
-          <t>23 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA62" s="1" t="n">
+        <v>10814.11</v>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
@@ -3900,10 +3729,8 @@
           <t>20 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>8 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF62" s="1" t="n">
+        <v>2212</v>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
@@ -3953,10 +3780,8 @@
           <t>80 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>55 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL64" s="1" t="n">
+        <v>13170</v>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
@@ -3976,10 +3801,8 @@
           <t>16 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>12 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ64" s="1" t="n">
+        <v>2754</v>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
@@ -3999,10 +3822,8 @@
           <t>125 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF64" t="inlineStr">
-        <is>
-          <t>62 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF64" s="1" t="n">
+        <v>260</v>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
@@ -4022,10 +3843,8 @@
           <t>168 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK64" t="inlineStr">
-        <is>
-          <t>96 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK64" s="1" t="n">
+        <v>14805</v>
       </c>
       <c r="BL64" t="inlineStr">
         <is>
@@ -4075,10 +3894,8 @@
           <t>161 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>121 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H66" s="1" t="n">
+        <v>1182.39</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4098,10 +3915,8 @@
           <t>146 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>105 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL66" s="1" t="n">
+        <v>2514.38</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
@@ -4121,10 +3936,8 @@
           <t>392 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>222 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ66" s="1" t="n">
+        <v>9898</v>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
@@ -4144,10 +3957,8 @@
           <t>240 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV66" t="inlineStr">
-        <is>
-          <t>152 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV66" s="1" t="n">
+        <v>5640</v>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
@@ -4167,10 +3978,8 @@
           <t>40 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK66" t="inlineStr">
-        <is>
-          <t>17 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK66" s="1" t="n">
+        <v>1237.29</v>
       </c>
       <c r="BL66" t="inlineStr">
         <is>
@@ -4220,10 +4029,8 @@
           <t>59 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>46 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W68" s="1" t="n">
+        <v>2146.67</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -4243,10 +4050,8 @@
           <t>96 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG68" s="1" t="n">
+        <v>13117.57</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -4266,10 +4071,8 @@
           <t>96 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>32 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ68" s="1" t="n">
+        <v>2741.81</v>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
@@ -4289,10 +4092,8 @@
           <t>24 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>8 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV68" s="1" t="n">
+        <v>10290</v>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
@@ -4312,10 +4113,8 @@
           <t>126 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF68" t="inlineStr">
-        <is>
-          <t>53 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF68" s="1" t="n">
+        <v>5933.56</v>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
@@ -4365,10 +4164,8 @@
           <t>190 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>81 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M70" s="1" t="n">
+        <v>994.4</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4388,10 +4185,8 @@
           <t>290 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>200 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB70" s="1" t="n">
+        <v>8855</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -4411,10 +4206,8 @@
           <t>234 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV70" t="inlineStr">
-        <is>
-          <t>176 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV70" s="1" t="n">
+        <v>2133</v>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
@@ -4434,10 +4227,8 @@
           <t>86 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF70" t="inlineStr">
-        <is>
-          <t>51 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF70" s="1" t="n">
+        <v>5709.66</v>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
@@ -4457,10 +4248,8 @@
           <t>52 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK70" t="inlineStr">
-        <is>
-          <t>34 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK70" s="1" t="n">
+        <v>570</v>
       </c>
       <c r="BL70" t="inlineStr">
         <is>
@@ -4510,10 +4299,8 @@
           <t>160 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>93 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R72" s="1" t="n">
+        <v>2983.02</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -4563,10 +4350,8 @@
           <t>94 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>35 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M74" s="1" t="n">
+        <v>1673.87</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -4586,10 +4371,8 @@
           <t>312 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>166 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL74" s="1" t="n">
+        <v>9116.219999999999</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
@@ -4609,10 +4392,8 @@
           <t>120 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>55 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ74" s="1" t="n">
+        <v>7402.23</v>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
@@ -4632,10 +4413,8 @@
           <t>117 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA74" t="inlineStr">
-        <is>
-          <t>61 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA74" s="1" t="n">
+        <v>402.24</v>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
@@ -4655,10 +4434,8 @@
           <t>116 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF74" t="inlineStr">
-        <is>
-          <t>74 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF74" s="1" t="n">
+        <v>8284.6</v>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
@@ -4708,10 +4485,8 @@
           <t>113 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>63 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ76" s="1" t="n">
+        <v>18355.91</v>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
@@ -4887,10 +4662,8 @@
           <t>336 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>160 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG80" s="1" t="n">
+        <v>2720</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -4910,10 +4683,8 @@
           <t>66 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA80" t="inlineStr">
-        <is>
-          <t>44 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA80" s="1" t="n">
+        <v>810</v>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
@@ -4933,10 +4704,8 @@
           <t>279 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF80" t="inlineStr">
-        <is>
-          <t>110 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF80" s="1" t="n">
+        <v>9825</v>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
@@ -4956,10 +4725,8 @@
           <t>58 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK80" t="inlineStr">
-        <is>
-          <t>34 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK80" s="1" t="n">
+        <v>8865</v>
       </c>
       <c r="BL80" t="inlineStr">
         <is>
@@ -5009,10 +4776,8 @@
           <t>121 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>96 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H82" s="1" t="n">
+        <v>938.09</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5032,10 +4797,8 @@
           <t>62 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>30 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M82" s="1" t="n">
+        <v>4050</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -5055,10 +4818,8 @@
           <t>29 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>9 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W82" s="1" t="n">
+        <v>2067.03</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -5078,10 +4839,8 @@
           <t>258 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>175 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL82" s="1" t="n">
+        <v>4190.62</v>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
@@ -5131,10 +4890,8 @@
           <t>107 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>78 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H84" s="1" t="n">
+        <v>834</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5154,10 +4911,8 @@
           <t>190 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ84" s="1" t="n">
+        <v>3900</v>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
@@ -5207,10 +4962,8 @@
           <t>79 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>60 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M86" s="1" t="n">
+        <v>736.6</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -5230,10 +4983,8 @@
           <t>47 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>32 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ86" s="1" t="n">
+        <v>4840</v>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
@@ -5283,10 +5034,8 @@
           <t>18 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV88" t="inlineStr">
-        <is>
-          <t>8 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV88" s="1" t="n">
+        <v>4570.67</v>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
@@ -5306,10 +5055,8 @@
           <t>120 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF88" t="inlineStr">
-        <is>
-          <t>84 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF88" s="1" t="n">
+        <v>600</v>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
@@ -5359,10 +5106,8 @@
           <t>121 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>86 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL90" s="1" t="n">
+        <v>4722.86</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
@@ -5382,10 +5127,8 @@
           <t>180 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>96 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ90" s="1" t="n">
+        <v>12920.26</v>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
@@ -5435,10 +5178,8 @@
           <t>148 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>89 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R92" s="1" t="n">
+        <v>2726.81</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -5458,10 +5199,8 @@
           <t>119 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>37 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL92" s="1" t="n">
+        <v>2031.93</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
@@ -5481,10 +5220,8 @@
           <t>165 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>97 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ92" s="1" t="n">
+        <v>1499.44</v>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
@@ -5504,10 +5241,8 @@
           <t>38 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV92" t="inlineStr">
-        <is>
-          <t>21 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV92" s="1" t="n">
+        <v>2025</v>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
@@ -5527,10 +5262,8 @@
           <t>268 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK92" t="inlineStr">
-        <is>
-          <t>190 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK92" s="1" t="n">
+        <v>5386.35</v>
       </c>
       <c r="BL92" t="inlineStr">
         <is>
@@ -5580,10 +5313,8 @@
           <t>192 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>97 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H94" s="1" t="n">
+        <v>1964.89</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5603,10 +5334,8 @@
           <t>11 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV94" t="inlineStr">
-        <is>
-          <t>4 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV94" s="1" t="n">
+        <v>1260</v>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
@@ -5626,10 +5355,8 @@
           <t>174 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK94" t="inlineStr">
-        <is>
-          <t>124 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK94" s="1" t="n">
+        <v>58803.64</v>
       </c>
       <c r="BL94" t="inlineStr">
         <is>
@@ -5679,10 +5406,8 @@
           <t>95 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>31 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M96" s="1" t="n">
+        <v>360</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5702,10 +5427,8 @@
           <t>99 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF96" t="inlineStr">
-        <is>
-          <t>31 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF96" s="1" t="n">
+        <v>19793</v>
       </c>
       <c r="BG96" t="inlineStr">
         <is>
@@ -5755,10 +5478,8 @@
           <t>143 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H98" s="1" t="n">
+        <v>3573</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5778,10 +5499,8 @@
           <t>26 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>20 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB98" s="1" t="n">
+        <v>4734</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -5801,10 +5520,8 @@
           <t>122 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>80 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ98" s="1" t="n">
+        <v>1584</v>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
@@ -5980,10 +5697,8 @@
           <t>56 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>17 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M102" s="1" t="n">
+        <v>7922</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -6003,10 +5718,8 @@
           <t>168 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>99 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R102" s="1" t="n">
+        <v>3033.19</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -6026,10 +5739,8 @@
           <t>92 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>50 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB102" s="1" t="n">
+        <v>4267</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -6049,10 +5760,8 @@
           <t>78 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>60 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL102" s="1" t="n">
+        <v>3295.02</v>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
@@ -6072,10 +5781,8 @@
           <t>196 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>82 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ102" s="1" t="n">
+        <v>1267.56</v>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
@@ -6095,10 +5802,8 @@
           <t>85 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA102" t="inlineStr">
-        <is>
-          <t>39 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA102" s="1" t="n">
+        <v>990</v>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
@@ -6118,10 +5823,8 @@
           <t>157 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK102" t="inlineStr">
-        <is>
-          <t>125 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK102" s="1" t="n">
+        <v>3543.65</v>
       </c>
       <c r="BL102" t="inlineStr">
         <is>
@@ -6171,10 +5874,8 @@
           <t>132 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>50 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H104" s="1" t="n">
+        <v>26448</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6194,10 +5895,8 @@
           <t>57 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>45 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M104" s="1" t="n">
+        <v>5340</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6217,10 +5916,8 @@
           <t>24 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>18 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB104" s="1" t="n">
+        <v>1265.95</v>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
@@ -6240,10 +5937,8 @@
           <t>194 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ104" s="1" t="n">
+        <v>18382</v>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
@@ -6263,10 +5958,8 @@
           <t>56 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV104" t="inlineStr">
-        <is>
-          <t>34 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV104" s="1" t="n">
+        <v>7334</v>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
@@ -6316,10 +6009,8 @@
           <t>254 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>189 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R106" s="1" t="n">
+        <v>3200</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -6339,10 +6030,8 @@
           <t>459 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK106" t="inlineStr">
-        <is>
-          <t>299 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK106" s="1" t="n">
+        <v>141792.65</v>
       </c>
       <c r="BL106" t="inlineStr">
         <is>
@@ -6406,10 +6095,8 @@
           <t>95 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF110" t="inlineStr">
-        <is>
-          <t>42 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF110" s="1" t="n">
+        <v>1021.51</v>
       </c>
       <c r="BG110" t="inlineStr">
         <is>
@@ -6459,10 +6146,8 @@
           <t>395 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>178 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M112" s="1" t="n">
+        <v>672.25</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -6482,10 +6167,8 @@
           <t>279 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>147 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R112" s="1" t="n">
+        <v>11776</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -6505,10 +6188,8 @@
           <t>514 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>182 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB112" s="1" t="n">
+        <v>1734.21</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -6528,10 +6209,8 @@
           <t>82 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF112" t="inlineStr">
-        <is>
-          <t>25 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF112" s="1" t="n">
+        <v>1935.27</v>
       </c>
       <c r="BG112" t="inlineStr">
         <is>
@@ -6551,10 +6230,8 @@
           <t>157 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK112" t="inlineStr">
-        <is>
-          <t>124 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK112" s="1" t="n">
+        <v>3825</v>
       </c>
       <c r="BL112" t="inlineStr">
         <is>
@@ -6604,10 +6281,8 @@
           <t>300 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>215 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H114" s="1" t="n">
+        <v>3829.93</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6627,10 +6302,8 @@
           <t>312 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>129 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M114" s="1" t="n">
+        <v>15635.23</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -6650,10 +6323,8 @@
           <t>47 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>19 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R114" s="1" t="n">
+        <v>4410</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -6673,10 +6344,8 @@
           <t>154 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>99 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB114" s="1" t="n">
+        <v>2720.35</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -6696,10 +6365,8 @@
           <t>11 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA114" t="inlineStr">
-        <is>
-          <t>5 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA114" s="1" t="n">
+        <v>2350.89</v>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
@@ -6719,10 +6386,8 @@
           <t>136 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK114" t="inlineStr">
-        <is>
-          <t>69 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK114" s="1" t="n">
+        <v>10530</v>
       </c>
       <c r="BL114" t="inlineStr">
         <is>
@@ -6772,10 +6437,8 @@
           <t>176 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>85 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M116" s="1" t="n">
+        <v>270.97</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -6795,10 +6458,8 @@
           <t>378 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>296 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG116" s="1" t="n">
+        <v>59735.41</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -6818,10 +6479,8 @@
           <t>162 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>87 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ116" s="1" t="n">
+        <v>7454.3</v>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
@@ -6841,10 +6500,8 @@
           <t>48 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA116" t="inlineStr">
-        <is>
-          <t>31 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA116" s="1" t="n">
+        <v>5439.98</v>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
@@ -6894,10 +6551,8 @@
           <t>113 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>39 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H118" s="1" t="n">
+        <v>14034.28</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -6917,10 +6572,8 @@
           <t>55 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>27 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG118" s="1" t="n">
+        <v>5448.84</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -6940,10 +6593,8 @@
           <t>137 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK118" t="inlineStr">
-        <is>
-          <t>83 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK118" s="1" t="n">
+        <v>55.69</v>
       </c>
       <c r="BL118" t="inlineStr">
         <is>
@@ -6993,10 +6644,8 @@
           <t>131 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>47 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W120" s="1" t="n">
+        <v>7057.72</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
@@ -7016,10 +6665,8 @@
           <t>80 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr">
-        <is>
-          <t>33 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL120" s="1" t="n">
+        <v>1496.62</v>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
@@ -7039,10 +6686,8 @@
           <t>281 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF120" t="inlineStr">
-        <is>
-          <t>160 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF120" s="1" t="n">
+        <v>29983</v>
       </c>
       <c r="BG120" t="inlineStr">
         <is>
@@ -7218,10 +6863,8 @@
           <t>343 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>120 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R124" s="1" t="n">
+        <v>14045.43</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -7241,10 +6884,8 @@
           <t>223 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>111 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG124" s="1" t="n">
+        <v>630.1900000000001</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -7264,10 +6905,8 @@
           <t>93 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV124" t="inlineStr">
-        <is>
-          <t>59 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV124" s="1" t="n">
+        <v>900</v>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
@@ -7317,10 +6956,8 @@
           <t>52 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>19 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H126" s="1" t="n">
+        <v>19670.32</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -7340,10 +6977,8 @@
           <t>45 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>18 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W126" s="1" t="n">
+        <v>484.97</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -7363,10 +6998,8 @@
           <t>68 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>25 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB126" s="1" t="n">
+        <v>1758.27</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
@@ -7386,10 +7019,8 @@
           <t>9 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>7 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG126" s="1" t="n">
+        <v>8608</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -7439,10 +7070,8 @@
           <t>51 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>24 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M128" s="1" t="n">
+        <v>2908.88</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -7462,10 +7091,8 @@
           <t>107 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>72 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB128" s="1" t="n">
+        <v>60</v>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
@@ -7485,10 +7112,8 @@
           <t>105 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL128" t="inlineStr">
-        <is>
-          <t>37 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL128" s="1" t="n">
+        <v>2031.93</v>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
@@ -7508,10 +7133,8 @@
           <t>25 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV128" t="inlineStr">
-        <is>
-          <t>17 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV128" s="1" t="n">
+        <v>22113</v>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
@@ -7531,10 +7154,8 @@
           <t>106 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA128" t="inlineStr">
-        <is>
-          <t>56 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA128" s="1" t="n">
+        <v>9827.059999999999</v>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
@@ -7554,10 +7175,8 @@
           <t>32 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF128" t="inlineStr">
-        <is>
-          <t>17 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF128" s="1" t="n">
+        <v>1752</v>
       </c>
       <c r="BG128" t="inlineStr">
         <is>
@@ -7607,10 +7226,8 @@
           <t>37 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>13 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R130" s="1" t="n">
+        <v>416.98</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -7630,10 +7247,8 @@
           <t>324 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA130" t="inlineStr">
-        <is>
-          <t>171 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA130" s="1" t="n">
+        <v>5380</v>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
@@ -7683,10 +7298,8 @@
           <t>171 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>107 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H132" s="1" t="n">
+        <v>756</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7706,10 +7319,8 @@
           <t>145 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>59 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M132" s="1" t="n">
+        <v>12887</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -7759,10 +7370,8 @@
           <t>34 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>24 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H134" s="1" t="n">
+        <v>234.52</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -7782,10 +7391,8 @@
           <t>163 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>94 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W134" s="1" t="n">
+        <v>21588.97</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
@@ -7805,10 +7412,8 @@
           <t>174 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF134" t="inlineStr">
-        <is>
-          <t>115 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF134" s="1" t="n">
+        <v>270</v>
       </c>
       <c r="BG134" t="inlineStr">
         <is>
@@ -7828,10 +7433,8 @@
           <t>243 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK134" t="inlineStr">
-        <is>
-          <t>116 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK134" s="1" t="n">
+        <v>8442.709999999999</v>
       </c>
       <c r="BL134" t="inlineStr">
         <is>
@@ -7881,10 +7484,8 @@
           <t>76 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>52 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG136" s="1" t="n">
+        <v>36.49</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -7904,10 +7505,8 @@
           <t>170 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>134 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ136" s="1" t="n">
+        <v>1095.98</v>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
@@ -7927,10 +7526,8 @@
           <t>124 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV136" t="inlineStr">
-        <is>
-          <t>77 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV136" s="1" t="n">
+        <v>3384.42</v>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
@@ -7950,10 +7547,8 @@
           <t>333 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF136" t="inlineStr">
-        <is>
-          <t>144 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF136" s="1" t="n">
+        <v>11147.17</v>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
@@ -8003,10 +7598,8 @@
           <t>65 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>31 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H138" s="1" t="n">
+        <v>12277</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -8026,10 +7619,8 @@
           <t>115 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>58 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R138" s="1" t="n">
+        <v>6788.63</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -8049,16 +7640,14 @@
           <t>46 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL138" t="inlineStr">
+      <c r="AL138" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM138" t="inlineStr">
         <is>
           <t>23 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>23 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
       <c r="AN138" t="inlineStr">
         <is>
           <t>46 ч. 0 мин. 0 с.</t>
@@ -8072,10 +7661,8 @@
           <t>156 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA138" t="inlineStr">
-        <is>
-          <t>91 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA138" s="1" t="n">
+        <v>1890</v>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
@@ -8125,10 +7712,8 @@
           <t>26 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV140" t="inlineStr">
-        <is>
-          <t>13 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV140" s="1" t="n">
+        <v>7427.33</v>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
@@ -8178,10 +7763,8 @@
           <t>38 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK142" t="inlineStr">
-        <is>
-          <t>19 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK142" s="1" t="n">
+        <v>11723</v>
       </c>
       <c r="BL142" t="inlineStr">
         <is>
@@ -8349,10 +7932,8 @@
           <t>75 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV146" t="inlineStr">
-        <is>
-          <t>58 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV146" s="1" t="n">
+        <v>19113.61</v>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
@@ -8402,10 +7983,8 @@
           <t>150 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>62 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG148" s="1" t="n">
+        <v>43.51</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -8425,10 +8004,8 @@
           <t>19 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>12 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL148" s="1" t="n">
+        <v>75</v>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
@@ -8448,10 +8025,8 @@
           <t>73 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA148" t="inlineStr">
-        <is>
-          <t>57 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA148" s="1" t="n">
+        <v>1515</v>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
@@ -8501,10 +8076,8 @@
           <t>19 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>15 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB150" s="1" t="n">
+        <v>1054.96</v>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
@@ -8524,10 +8097,8 @@
           <t>130 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF150" t="inlineStr">
-        <is>
-          <t>103 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF150" s="1" t="n">
+        <v>11531.27</v>
       </c>
       <c r="BG150" t="inlineStr">
         <is>
@@ -8577,10 +8148,8 @@
           <t>198 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>103 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H152" s="1" t="n">
+        <v>8296</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -8600,10 +8169,8 @@
           <t>120 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>57 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W152" s="1" t="n">
+        <v>2555</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
@@ -8623,10 +8190,8 @@
           <t>65 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF152" t="inlineStr">
-        <is>
-          <t>39 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF152" s="1" t="n">
+        <v>10405</v>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
@@ -8676,10 +8241,8 @@
           <t>298 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>96 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M154" s="1" t="n">
+        <v>306.04</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
@@ -8699,10 +8262,8 @@
           <t>232 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>91 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R154" s="1" t="n">
+        <v>2869</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -8722,10 +8283,8 @@
           <t>185 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>131 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG154" s="1" t="n">
+        <v>26436.96</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -8745,10 +8304,8 @@
           <t>197 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>67 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL154" s="1" t="n">
+        <v>2676.31</v>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
@@ -8768,10 +8325,8 @@
           <t>198 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA154" t="inlineStr">
-        <is>
-          <t>111 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA154" s="1" t="n">
+        <v>19478.63</v>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
@@ -8821,10 +8376,8 @@
           <t>160 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>110 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H156" s="1" t="n">
+        <v>2179.44</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -8844,10 +8397,8 @@
           <t>193 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA156" t="inlineStr">
-        <is>
-          <t>116 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA156" s="1" t="n">
+        <v>2306.3</v>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
@@ -8897,10 +8448,8 @@
           <t>130 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>82 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M158" s="1" t="n">
+        <v>3921.64</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -8920,10 +8469,8 @@
           <t>21 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB158" s="1" t="n">
+        <v>2880</v>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
@@ -8943,10 +8490,8 @@
           <t>190 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV158" t="inlineStr">
-        <is>
-          <t>152 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV158" s="1" t="n">
+        <v>2828.92</v>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
@@ -8966,10 +8511,8 @@
           <t>45 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA158" t="inlineStr">
-        <is>
-          <t>29 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA158" s="1" t="n">
+        <v>191.23</v>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
@@ -9019,10 +8562,8 @@
           <t>142 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>97 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M160" s="1" t="n">
+        <v>3216</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
@@ -9042,10 +8583,8 @@
           <t>103 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>46 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W160" s="1" t="n">
+        <v>385</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
@@ -9065,10 +8604,8 @@
           <t>104 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>59 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB160" s="1" t="n">
+        <v>390</v>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
@@ -9088,10 +8625,8 @@
           <t>107 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>68 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG160" s="1" t="n">
+        <v>445</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -9111,10 +8646,8 @@
           <t>125 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>75 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL160" s="1" t="n">
+        <v>4118.77</v>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
@@ -9134,10 +8667,8 @@
           <t>291 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK160" t="inlineStr">
-        <is>
-          <t>94 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK160" s="1" t="n">
+        <v>5040</v>
       </c>
       <c r="BL160" t="inlineStr">
         <is>
@@ -9187,10 +8718,8 @@
           <t>194 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>117 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M162" s="1" t="n">
+        <v>1866</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
@@ -9210,10 +8739,8 @@
           <t>158 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>66 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R162" s="1" t="n">
+        <v>3740</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -9233,10 +8760,8 @@
           <t>315 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>237 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB162" s="1" t="n">
+        <v>27905</v>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
@@ -9256,10 +8781,8 @@
           <t>157 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA162" t="inlineStr">
-        <is>
-          <t>87 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA162" s="1" t="n">
+        <v>15267.03</v>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
@@ -9309,10 +8832,8 @@
           <t>14 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>8 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R164" s="1" t="n">
+        <v>1584</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -9332,10 +8853,8 @@
           <t>287 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>160 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB164" s="1" t="n">
+        <v>17764</v>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
@@ -9355,10 +8874,8 @@
           <t>22 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF164" t="inlineStr">
-        <is>
-          <t>17 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF164" s="1" t="n">
+        <v>1903.22</v>
       </c>
       <c r="BG164" t="inlineStr">
         <is>
@@ -9378,10 +8895,8 @@
           <t>177 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK164" t="inlineStr">
-        <is>
-          <t>135 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK164" s="1" t="n">
+        <v>64020.09</v>
       </c>
       <c r="BL164" t="inlineStr">
         <is>
@@ -9557,10 +9072,8 @@
           <t>337 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>211 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M168" s="1" t="n">
+        <v>11334</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -9580,10 +9093,8 @@
           <t>31 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>14 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R168" s="1" t="n">
+        <v>6636</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -9603,10 +9114,8 @@
           <t>140 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>52 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W168" s="1" t="n">
+        <v>1401.03</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -9626,10 +9135,8 @@
           <t>92 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>28 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB168" s="1" t="n">
+        <v>1969.26</v>
       </c>
       <c r="AC168" t="inlineStr">
         <is>
@@ -9649,10 +9156,8 @@
           <t>112 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>74 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ168" s="1" t="n">
+        <v>9959.370000000001</v>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
@@ -9702,10 +9207,8 @@
           <t>94 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>33 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R170" s="1" t="n">
+        <v>15102</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -9725,10 +9228,8 @@
           <t>242 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>75 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W170" s="1" t="n">
+        <v>24066</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -9778,10 +9279,8 @@
           <t>52 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>29 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M172" s="1" t="n">
+        <v>92.45</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -9801,10 +9300,8 @@
           <t>338 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>167 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W172" s="1" t="n">
+        <v>7793.33</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
@@ -9824,10 +9321,8 @@
           <t>161 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>50 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL172" s="1" t="n">
+        <v>1997.24</v>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
@@ -9847,10 +9342,8 @@
           <t>72 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>48 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ172" s="1" t="n">
+        <v>4112.72</v>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
@@ -9870,10 +9363,8 @@
           <t>148 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA172" t="inlineStr">
-        <is>
-          <t>69 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA172" s="1" t="n">
+        <v>12108.34</v>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
@@ -9923,10 +9414,8 @@
           <t>38 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>26 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H174" s="1" t="n">
+        <v>3154.56</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -9946,10 +9435,8 @@
           <t>16 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>11 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB174" s="1" t="n">
+        <v>104.81</v>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
@@ -9969,10 +9456,8 @@
           <t>210 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF174" t="inlineStr">
-        <is>
-          <t>167 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF174" s="1" t="n">
+        <v>12927.62</v>
       </c>
       <c r="BG174" t="inlineStr">
         <is>
@@ -10022,10 +9507,8 @@
           <t>41 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>20 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M176" s="1" t="n">
+        <v>956.5</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -10045,10 +9528,8 @@
           <t>174 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>81 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R176" s="1" t="n">
+        <v>956.52</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -10068,10 +9549,8 @@
           <t>150 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>112 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG176" s="1" t="n">
+        <v>2970</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -10091,10 +9570,8 @@
           <t>304 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>167 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ176" s="1" t="n">
+        <v>22475.88</v>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
@@ -10114,10 +9591,8 @@
           <t>212 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV176" t="inlineStr">
-        <is>
-          <t>149 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV176" s="1" t="n">
+        <v>2773.08</v>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
@@ -10137,10 +9612,8 @@
           <t>19 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA176" t="inlineStr">
-        <is>
-          <t>11 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA176" s="1" t="n">
+        <v>72.53</v>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
@@ -10160,10 +9633,8 @@
           <t>111 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF176" t="inlineStr">
-        <is>
-          <t>51 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF176" s="1" t="n">
+        <v>5709.66</v>
       </c>
       <c r="BG176" t="inlineStr">
         <is>
@@ -10213,10 +9684,8 @@
           <t>73 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>58 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ178" s="1" t="n">
+        <v>7805.99</v>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
@@ -10236,10 +9705,8 @@
           <t>569 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA178" t="inlineStr">
-        <is>
-          <t>192 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA178" s="1" t="n">
+        <v>33692.76</v>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
@@ -10289,10 +9756,8 @@
           <t>137 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>106 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H180" s="1" t="n">
+        <v>1845</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -10312,10 +9777,8 @@
           <t>11 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>4 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W180" s="1" t="n">
+        <v>3260</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
@@ -10335,10 +9798,8 @@
           <t>76 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>37 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB180" s="1" t="n">
+        <v>2780</v>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
@@ -10358,10 +9819,8 @@
           <t>154 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV180" t="inlineStr">
-        <is>
-          <t>105 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV180" s="1" t="n">
+        <v>3740</v>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
@@ -10411,10 +9870,8 @@
           <t>102 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>50 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W182" s="1" t="n">
+        <v>7508.21</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
@@ -10434,10 +9891,8 @@
           <t>180 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV182" t="inlineStr">
-        <is>
-          <t>136 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV182" s="1" t="n">
+        <v>44818.12</v>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
@@ -10457,10 +9912,8 @@
           <t>93 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK182" t="inlineStr">
-        <is>
-          <t>70 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK182" s="1" t="n">
+        <v>33195.6</v>
       </c>
       <c r="BL182" t="inlineStr">
         <is>
@@ -10510,10 +9963,8 @@
           <t>67 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>32 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W184" s="1" t="n">
+        <v>1764</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
@@ -10533,10 +9984,8 @@
           <t>171 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>112 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL184" s="1" t="n">
+        <v>3388</v>
       </c>
       <c r="AM184" t="inlineStr">
         <is>
@@ -10556,10 +10005,8 @@
           <t>258 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>180 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ184" s="1" t="n">
+        <v>792</v>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
@@ -10609,10 +10056,8 @@
           <t>9 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>5 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H186" s="1" t="n">
+        <v>101.28</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -10632,10 +10077,8 @@
           <t>112 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R186" t="inlineStr">
-        <is>
-          <t>68 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R186" s="1" t="n">
+        <v>1595</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -10655,10 +10098,8 @@
           <t>435 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>245 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG186" s="1" t="n">
+        <v>49443.16</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -10678,10 +10119,8 @@
           <t>165 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL186" t="inlineStr">
-        <is>
-          <t>56 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL186" s="1" t="n">
+        <v>2430</v>
       </c>
       <c r="AM186" t="inlineStr">
         <is>
@@ -10701,10 +10140,8 @@
           <t>390 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>205 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ186" s="1" t="n">
+        <v>2970</v>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
@@ -10724,10 +10161,8 @@
           <t>157 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF186" t="inlineStr">
-        <is>
-          <t>97 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF186" s="1" t="n">
+        <v>10859.54</v>
       </c>
       <c r="BG186" t="inlineStr">
         <is>
@@ -10895,10 +10330,8 @@
           <t>72 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>55 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M190" s="1" t="n">
+        <v>3874</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -10918,10 +10351,8 @@
           <t>170 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>72 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R190" s="1" t="n">
+        <v>3980</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -10941,10 +10372,8 @@
           <t>68 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF190" t="inlineStr">
-        <is>
-          <t>43 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF190" s="1" t="n">
+        <v>4044</v>
       </c>
       <c r="BG190" t="inlineStr">
         <is>
@@ -10964,10 +10393,8 @@
           <t>123 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK190" t="inlineStr">
-        <is>
-          <t>89 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK190" s="1" t="n">
+        <v>3740</v>
       </c>
       <c r="BL190" t="inlineStr">
         <is>
@@ -11017,10 +10444,8 @@
           <t>10 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>3 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M192" s="1" t="n">
+        <v>277.66</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
@@ -11040,10 +10465,8 @@
           <t>86 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>53 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG192" s="1" t="n">
+        <v>1737.22</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -11063,10 +10486,8 @@
           <t>197 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA192" t="inlineStr">
-        <is>
-          <t>138 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA192" s="1" t="n">
+        <v>2743.7</v>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
@@ -11116,10 +10537,8 @@
           <t>148 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>108 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ194" s="1" t="n">
+        <v>883.33</v>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
@@ -11139,10 +10558,8 @@
           <t>89 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV194" t="inlineStr">
-        <is>
-          <t>43 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV194" s="1" t="n">
+        <v>1890</v>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
@@ -11192,10 +10609,8 @@
           <t>35 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>16 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ196" s="1" t="n">
+        <v>432</v>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
@@ -11215,10 +10630,8 @@
           <t>102 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF196" t="inlineStr">
-        <is>
-          <t>57 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF196" s="1" t="n">
+        <v>795</v>
       </c>
       <c r="BG196" t="inlineStr">
         <is>
@@ -11268,10 +10681,8 @@
           <t>206 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>161 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R198" s="1" t="n">
+        <v>18844.29</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -11291,10 +10702,8 @@
           <t>132 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>71 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ198" s="1" t="n">
+        <v>9555.610000000001</v>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
@@ -11314,10 +10723,8 @@
           <t>88 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA198" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA198" s="1" t="n">
+        <v>11406.4</v>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
@@ -11337,10 +10744,8 @@
           <t>154 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF198" t="inlineStr">
-        <is>
-          <t>74 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF198" s="1" t="n">
+        <v>8284.6</v>
       </c>
       <c r="BG198" t="inlineStr">
         <is>
@@ -11390,10 +10795,8 @@
           <t>59 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>47 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG200" s="1" t="n">
+        <v>5130</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -11413,10 +10816,8 @@
           <t>244 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV200" t="inlineStr">
-        <is>
-          <t>170 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV200" s="1" t="n">
+        <v>4140</v>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
@@ -11436,10 +10837,8 @@
           <t>304 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF200" t="inlineStr">
-        <is>
-          <t>121 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF200" s="1" t="n">
+        <v>13546.44</v>
       </c>
       <c r="BG200" t="inlineStr">
         <is>
@@ -11489,10 +10888,8 @@
           <t>447 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK202" t="inlineStr">
-        <is>
-          <t>201 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK202" s="1" t="n">
+        <v>4285</v>
       </c>
       <c r="BL202" t="inlineStr">
         <is>
@@ -11542,10 +10939,8 @@
           <t>108 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>71 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M204" s="1" t="n">
+        <v>2364</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
@@ -11565,10 +10960,8 @@
           <t>76 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>48 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W204" s="1" t="n">
+        <v>12405</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
@@ -11588,10 +10981,8 @@
           <t>355 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>248 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB204" s="1" t="n">
+        <v>2500</v>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
@@ -11611,10 +11002,8 @@
           <t>139 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>44 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG204" s="1" t="n">
+        <v>249.81</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -11634,10 +11023,8 @@
           <t>315 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>217 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ204" s="1" t="n">
+        <v>29205.18</v>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
@@ -11657,10 +11044,8 @@
           <t>118 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA204" t="inlineStr">
-        <is>
-          <t>45 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA204" s="1" t="n">
+        <v>6600</v>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
@@ -11710,10 +11095,8 @@
           <t>33 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>21 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H206" s="1" t="n">
+        <v>750</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -11733,56 +11116,50 @@
           <t>51 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr">
+      <c r="R206" s="1" t="n">
+        <v>1530</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>35 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>51 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AO206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>184 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AQ206" s="1" t="n">
+        <v>39334.09</v>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>49 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>184 ч. 0 мин. 0 с.</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU206" t="inlineStr">
         <is>
           <t>16 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>35 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>51 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AO206" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP206" t="inlineStr">
-        <is>
-          <t>184 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>135 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>49 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>184 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AT206" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>16 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
-      <c r="AV206" t="inlineStr">
-        <is>
-          <t>6 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV206" s="1" t="n">
+        <v>12481</v>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
@@ -11832,10 +11209,8 @@
           <t>142 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>68 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="W208" s="1" t="n">
+        <v>920</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
@@ -11855,10 +11230,8 @@
           <t>145 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>90 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB208" s="1" t="n">
+        <v>6500</v>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
@@ -11878,10 +11251,8 @@
           <t>187 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK208" t="inlineStr">
-        <is>
-          <t>83 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK208" s="1" t="n">
+        <v>6930</v>
       </c>
       <c r="BL208" t="inlineStr">
         <is>
@@ -12049,10 +11420,8 @@
           <t>493 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>383 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB212" s="1" t="n">
+        <v>26936.69</v>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
@@ -12072,10 +11441,8 @@
           <t>61 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>27 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG212" s="1" t="n">
+        <v>5448.84</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -12095,10 +11462,8 @@
           <t>72 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>38 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL212" s="1" t="n">
+        <v>1723.38</v>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
@@ -12118,10 +11483,8 @@
           <t>281 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK212" t="inlineStr">
-        <is>
-          <t>104 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK212" s="1" t="n">
+        <v>49319.18</v>
       </c>
       <c r="BL212" t="inlineStr">
         <is>
@@ -12171,10 +11534,8 @@
           <t>24 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV214" t="inlineStr">
-        <is>
-          <t>16 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV214" s="1" t="n">
+        <v>5272.72</v>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
@@ -12194,10 +11555,8 @@
           <t>168 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK214" t="inlineStr">
-        <is>
-          <t>129 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK214" s="1" t="n">
+        <v>12804</v>
       </c>
       <c r="BL214" t="inlineStr">
         <is>
@@ -12247,10 +11606,8 @@
           <t>98 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>39 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="H216" s="1" t="n">
+        <v>20637</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -12270,10 +11627,8 @@
           <t>134 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>83 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M216" s="1" t="n">
+        <v>41462</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -12293,10 +11648,8 @@
           <t>43 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>25 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R216" s="1" t="n">
+        <v>3780</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -12316,10 +11669,8 @@
           <t>188 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>142 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB216" s="1" t="n">
+        <v>720</v>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
@@ -12339,10 +11690,8 @@
           <t>38 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL216" t="inlineStr">
-        <is>
-          <t>29 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL216" s="1" t="n">
+        <v>1592.59</v>
       </c>
       <c r="AM216" t="inlineStr">
         <is>
@@ -12362,10 +11711,8 @@
           <t>245 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>134 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ216" s="1" t="n">
+        <v>27859</v>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
@@ -12385,10 +11732,8 @@
           <t>385 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV216" t="inlineStr">
-        <is>
-          <t>294 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV216" s="1" t="n">
+        <v>4895</v>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
@@ -12408,10 +11753,8 @@
           <t>6 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA216" t="inlineStr">
-        <is>
-          <t>4 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA216" s="1" t="n">
+        <v>5225</v>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
@@ -12431,10 +11774,8 @@
           <t>179 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK216" t="inlineStr">
-        <is>
-          <t>142 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK216" s="1" t="n">
+        <v>19760</v>
       </c>
       <c r="BL216" t="inlineStr">
         <is>
@@ -12484,10 +11825,8 @@
           <t>342 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>183 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="R218" s="1" t="n">
+        <v>21419.28</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -12507,10 +11846,8 @@
           <t>159 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA218" t="inlineStr">
-        <is>
-          <t>93 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA218" s="1" t="n">
+        <v>1064</v>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
@@ -12530,10 +11867,8 @@
           <t>38 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF218" t="inlineStr">
-        <is>
-          <t>28 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF218" s="1" t="n">
+        <v>685.71</v>
       </c>
       <c r="BG218" t="inlineStr">
         <is>
@@ -12553,10 +11888,8 @@
           <t>166 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK218" t="inlineStr">
-        <is>
-          <t>93 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK218" s="1" t="n">
+        <v>44102.73</v>
       </c>
       <c r="BL218" t="inlineStr">
         <is>
@@ -12606,10 +11939,8 @@
           <t>191 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV220" t="inlineStr">
-        <is>
-          <t>86 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV220" s="1" t="n">
+        <v>28340.87</v>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
@@ -12629,10 +11960,8 @@
           <t>6 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BA220" t="inlineStr">
-        <is>
-          <t>4 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BA220" s="1" t="n">
+        <v>701.9299999999999</v>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
@@ -12682,10 +12011,8 @@
           <t>142 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>65 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AB222" s="1" t="n">
+        <v>998.78</v>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
@@ -12705,10 +12032,8 @@
           <t>124 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>75 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AL222" s="1" t="n">
+        <v>4118.77</v>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
@@ -12728,10 +12053,8 @@
           <t>123 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF222" t="inlineStr">
-        <is>
-          <t>62 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF222" s="1" t="n">
+        <v>330.67</v>
       </c>
       <c r="BG222" t="inlineStr">
         <is>
@@ -12781,10 +12104,8 @@
           <t>175 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>60 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG224" s="1" t="n">
+        <v>1243.75</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -12804,10 +12125,8 @@
           <t>19 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>11 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ224" s="1" t="n">
+        <v>189.34</v>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
@@ -12857,10 +12176,8 @@
           <t>93 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AV226" t="inlineStr">
-        <is>
-          <t>52 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AV226" s="1" t="n">
+        <v>2285.58</v>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
@@ -12910,16 +12227,14 @@
           <t>146 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H228" s="1" t="n">
+        <v>355</v>
+      </c>
+      <c r="I228" t="inlineStr">
         <is>
           <t>73 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>73 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
       <c r="J228" t="inlineStr">
         <is>
           <t>146 ч. 0 мин. 0 с.</t>
@@ -12933,10 +12248,8 @@
           <t>150 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>88 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="M228" s="1" t="n">
+        <v>280.54</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -12956,10 +12269,8 @@
           <t>562 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>188 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AG228" s="1" t="n">
+        <v>37940.06</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -12979,16 +12290,14 @@
           <t>20 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AL228" t="inlineStr">
+      <c r="AL228" s="1" t="n">
+        <v>399.45</v>
+      </c>
+      <c r="AM228" t="inlineStr">
         <is>
           <t>10 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>10 ч. 0 мин. 0 с.</t>
-        </is>
-      </c>
       <c r="AN228" t="inlineStr">
         <is>
           <t>20 ч. 0 мин. 0 с.</t>
@@ -13002,10 +12311,8 @@
           <t>154 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>122 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ228" s="1" t="n">
+        <v>10453.16</v>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
@@ -13025,10 +12332,8 @@
           <t>237 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BF228" t="inlineStr">
-        <is>
-          <t>174 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BF228" s="1" t="n">
+        <v>19480</v>
       </c>
       <c r="BG228" t="inlineStr">
         <is>
@@ -13048,10 +12353,8 @@
           <t>155 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="BK228" t="inlineStr">
-        <is>
-          <t>99 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="BK228" s="1" t="n">
+        <v>16604</v>
       </c>
       <c r="BL228" t="inlineStr">
         <is>
@@ -13101,10 +12404,8 @@
           <t>48 ч. 0 мин. 0 с.</t>
         </is>
       </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>14 ч. 0 мин. 0 с.</t>
-        </is>
+      <c r="AQ230" s="1" t="n">
+        <v>965</v>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
